--- a/templates/ht_cn/hetong-Header.xlsx
+++ b/templates/ht_cn/hetong-Header.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>电子元器件采购合同</t>
   </si>
@@ -243,6 +243,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>品名</t>
     </r>
     <r>
@@ -341,13 +348,28 @@
 Remark</t>
   </si>
   <si>
-    <t>Z-6039</t>
-  </si>
-  <si>
-    <t>MURATA</t>
+    <t>RFCA8828SR</t>
+  </si>
+  <si>
+    <t>QORVO</t>
   </si>
   <si>
     <t>pcs</t>
+  </si>
+  <si>
+    <t>LMC7101AIM5X/NOPB</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>TCA6408 APWR</t>
+  </si>
+  <si>
+    <t>SRV05-4MR6T1G</t>
+  </si>
+  <si>
+    <t>TECH PUBLIC</t>
   </si>
 </sst>
 </file>
@@ -360,7 +382,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,6 +441,12 @@
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -956,133 +984,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1122,7 +1150,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1471,7 +1499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.6363636363636" customWidth="1"/>
@@ -1716,7 +1744,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" ht="19" customHeight="1" spans="1:8">
+    <row r="22" ht="26" customHeight="1" spans="1:8">
       <c r="A22" s="15">
         <v>1</v>
       </c>
@@ -1730,121 +1758,94 @@
         <v>37</v>
       </c>
       <c r="E22" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F22" s="15">
-        <v>11.5</v>
+        <v>32.1</v>
       </c>
       <c r="G22" s="15">
-        <f>F22*E22</f>
-        <v>920</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1" spans="1:8">
+        <v>3212.9</v>
+      </c>
+      <c r="H22" s="15">
+        <v>3212.9</v>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1" spans="1:8">
       <c r="A23" s="15">
         <v>2</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1" spans="1:8">
+        <v>37</v>
+      </c>
+      <c r="E23" s="15">
+        <v>2500</v>
+      </c>
+      <c r="F23" s="15">
+        <v>2.8</v>
+      </c>
+      <c r="G23" s="15">
+        <v>6885</v>
+      </c>
+      <c r="H23" s="15">
+        <v>6885</v>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1" spans="1:8">
       <c r="A24" s="15">
         <v>3</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" ht="19" customHeight="1" spans="1:8">
+        <v>37</v>
+      </c>
+      <c r="E24" s="15">
+        <v>50</v>
+      </c>
+      <c r="F24" s="15">
+        <v>3</v>
+      </c>
+      <c r="G24" s="15">
+        <v>151.4</v>
+      </c>
+      <c r="H24" s="15">
+        <v>151.45</v>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1" spans="1:8">
       <c r="A25" s="15">
         <v>4</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1" spans="1:8">
-      <c r="A26" s="15">
-        <v>5</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>8</v>
+        <v>37</v>
+      </c>
+      <c r="E25" s="15">
+        <v>50</v>
+      </c>
+      <c r="F25" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G25" s="15">
+        <v>21.8</v>
+      </c>
+      <c r="H25" s="15">
+        <v>21.8</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ht_cn/hetong-Header.xlsx
+++ b/templates/ht_cn/hetong-Header.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="20150" windowHeight="9880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -89,125 +89,16 @@
     <t>公司名称（内地注册）:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>深圳欣亿扬微科技有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>深圳市福田区华强北街道华航社区华强</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>北路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1019</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>号华强广场</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>座</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">6I-6J
-</t>
-    </r>
+    <t>深圳市盛芯烁科技有限公司</t>
+  </si>
+  <si>
+    <t>深圳市福田区华强北街道华航社区深南中3018号都会轩1112</t>
   </si>
   <si>
     <t>统一社会信用代码:</t>
   </si>
   <si>
-    <t>xfdsfdsafds</t>
+    <t>91440300MAD3ALP20C</t>
   </si>
   <si>
     <r>
@@ -230,10 +121,10 @@
     </r>
   </si>
   <si>
-    <t>杨燕如</t>
-  </si>
-  <si>
-    <t>+86 17768593621</t>
+    <t>钟丽贤</t>
+  </si>
+  <si>
+    <t>+86 18576446888</t>
   </si>
   <si>
     <t>▌ 第一条 采购货物明细 Goods Details</t>
